--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260611.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>555,720,000</t>
+          <t>574,340,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.67%</t>
+          <t>13.40%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>669,730,000</t>
+          <t>667,080,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.45%</t>
+          <t>12.47%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>909,417,000</t>
+          <t>899,717,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.54%</t>
+          <t>11.29%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>144,330,000</t>
+          <t>162,670,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.22%</t>
+          <t>11.19%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.01%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,060,000</t>
+          <t>34,700,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>5.06%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>102,213,000</t>
+          <t>101,143,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>41,195,000</t>
+          <t>765,470,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>684,320,000</t>
+          <t>41,195,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,350,000</t>
+          <t>21,630,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -836,117 +836,117 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>274,224,000</t>
+          <t>109,950,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>98,520,000</t>
+          <t>269,844,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>73,012,000</t>
+          <t>11,400,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>10,180,000</t>
+          <t>68,460,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,090,000</t>
+          <t>63,910,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,910,000</t>
+          <t>203,680,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>56,760,000</t>
+          <t>26,430,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1041,66 +1041,66 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>181,870,000</t>
+          <t>11,948,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10,478,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>116,010,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1117,34 +1117,34 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,014,000</t>
+          <t>9,514,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>103,540,000</t>
+          <t>13,060,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1161,78 +1161,78 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>64,550,000</t>
+          <t>72,220,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>11,610,000</t>
+          <t>75,070,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>33,440,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>66,150,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1249,34 +1249,34 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>39,730,000</t>
+          <t>37,230,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>14,010,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1293,78 +1293,78 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>24,560,000</t>
+          <t>27,490,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>27,720,000</t>
+          <t>27,329,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>27,549,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>12,530,000</t>
+          <t>29,560,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,950,000</t>
+          <t>15,750,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,22 +1393,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>26,440,000</t>
+          <t>40,840,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1437,44 +1437,44 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>36,530,000</t>
+          <t>26,666,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>26,666,000</t>
+          <t>19,910,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1503,176 +1503,176 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>19,910,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,290,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>28,990,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,654,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,176,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,602,441</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,599,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>5,520,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1689,144 +1689,144 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>5,381,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,980,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,990,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2,250,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,710,000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>台灣虎航</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>3,330,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1843,56 +1843,56 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>3,470,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>台灣虎航</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>3,396,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>342,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>5,575,901,251</t>
+          <t>7,704,030,740</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,934,523,117</t>
+          <t>1,897,108,717</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,886,813,201</t>
+          <t>1,152,705,471</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
